--- a/feedback_forms/022_employee_suggestion_submission_form--feedback_forms.xlsx
+++ b/feedback_forms/022_employee_suggestion_submission_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,41 +520,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_1</t>
+          <t>suggestion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>submit_form</t>
+          <t>Suggestion</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_2</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>suggestions</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,41 +566,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_3</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>suggestion</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_4</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,64 +612,64 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_5</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_6</t>
+          <t>submit_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>suggestion_description</t>
+          <t>Submit Date</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_7</t>
+          <t>submit_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>name_email</t>
+          <t>Submit Time</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,409 +681,64 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_8</t>
+          <t>submission_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Submission Status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_9</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Submission Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_10</t>
+          <t>submission_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>submit_and_save</t>
+          <t>Submission Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>form_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>form_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>suggestion_date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>submit_date</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>form_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>submit_form_date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>submit_form_suggestion_date</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>suggestion_submit_date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>suggestion_submit</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>submission_status</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>suggestion_submit_date</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>suggestion</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,357 +781,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>id_1</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>id_1</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>id_2</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>id_2</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>id_3</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>id_3</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>submission</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>Submission</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>marketing</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>form_8_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>submit_and_save</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>submit_and_save</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>form_8_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>save</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>save</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>form_8_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>form_10_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>submit_and_save</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>submit_and_save</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>form_10_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>save</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>save</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>form_10_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>form_14_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>submit_date</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>submit_date</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>form_14_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>save</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>save</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>form_14_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>form_20_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>form_20_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>save</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>save</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>form_20_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>reset</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>form_22_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>submission_status</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>submission_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>form_22_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>form_22_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
